--- a/users/excel/sample.xlsx
+++ b/users/excel/sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\pmss\users\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F219B3-9D25-4DF2-A07E-E2AD4F2640F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80114D2F-8CFA-420B-8C3A-B07AD6032FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4860" yWindow="2835" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لیست بیمه شدگان" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="330">
   <si>
     <t>ردیف بیمه شده</t>
   </si>
@@ -1019,36 +1019,6 @@
   </si>
   <si>
     <t>IR</t>
-  </si>
-  <si>
-    <t>آروین</t>
-  </si>
-  <si>
-    <t>کورنگ بهشتی</t>
-  </si>
-  <si>
-    <t>احمد</t>
-  </si>
-  <si>
-    <t>1377/05/09</t>
-  </si>
-  <si>
-    <t>1272715434</t>
-  </si>
-  <si>
-    <t>1404/07/12</t>
-  </si>
-  <si>
-    <t>اصفهان مقدم</t>
-  </si>
-  <si>
-    <t>حسن</t>
-  </si>
-  <si>
-    <t>1343/12/27</t>
-  </si>
-  <si>
-    <t>1282828282</t>
   </si>
 </sst>
 </file>
@@ -1479,7 +1449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1608,151 +1578,6 @@
       </c>
       <c r="AE1" s="5" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="B2">
-        <v>4040</v>
-      </c>
-      <c r="C2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="J2">
-        <v>1272715434</v>
-      </c>
-      <c r="L2">
-        <v>9136304789</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>3</v>
-      </c>
-      <c r="O2">
-        <v>3</v>
-      </c>
-      <c r="P2" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q2">
-        <v>5</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>65666666</v>
-      </c>
-      <c r="T2" t="s">
-        <v>329</v>
-      </c>
-      <c r="U2">
-        <v>44444444444444</v>
-      </c>
-      <c r="V2">
-        <v>2</v>
-      </c>
-      <c r="X2">
-        <v>4040</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>336</v>
-      </c>
-      <c r="AE2">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="B3">
-        <v>4040</v>
-      </c>
-      <c r="C3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D3" t="s">
-        <v>331</v>
-      </c>
-      <c r="E3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="J3">
-        <v>302</v>
-      </c>
-      <c r="L3">
-        <v>9192215634</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-      <c r="N3">
-        <v>2</v>
-      </c>
-      <c r="O3">
-        <v>3</v>
-      </c>
-      <c r="Q3">
-        <v>5</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>55555555</v>
-      </c>
-      <c r="T3" t="s">
-        <v>329</v>
-      </c>
-      <c r="U3">
-        <v>6.4565446546565402E+17</v>
-      </c>
-      <c r="V3">
-        <v>1</v>
-      </c>
-      <c r="X3">
-        <v>4040</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>336</v>
-      </c>
-      <c r="AE3">
-        <v>999</v>
       </c>
     </row>
   </sheetData>
